--- a/app/reports/GECC_research.xlsx
+++ b/app/reports/GECC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-14 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.385</v>
+        <v>5.495</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04586999893188477</v>
+        <v>0.04549000263214111</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>13892045.31104921</v>
+        <v>13892044.40400364</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>5.385</v>
+        <v>5.495</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>74808664</v>
+        <v>76336784</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>79458576</v>
+        <v>79735160</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.485849</v>
+        <v>9.518867999999999</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>4.099</v>
+        <v>4.065</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.415</v>
+        <v>1.403</v>
       </c>
     </row>
     <row r="8">
@@ -1557,14 +1557,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>6309846016</v>
+        <v>6831612928</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-64.51900000000001</v>
+        <v>-68.764</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>638.678</v>
+        <v>680.705</v>
       </c>
     </row>
     <row r="9">
@@ -1595,12 +1595,12 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>48099104</v>
+        <v>49036972</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>6.231</v>
+        <v>6.238</v>
       </c>
     </row>
     <row r="11">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C11" s="32" t="n"/>
       <c r="D11" s="33" t="n">
-        <v>16.22224</v>
+        <v>16.167612</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
@@ -1633,12 +1633,12 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>82753928</v>
+        <v>85034592</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>9.194000000000001</v>
+        <v>9.441000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>48989548</v>
+        <v>44935904</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-2.879</v>
+        <v>-2.799</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-7.132</v>
+        <v>-6.934</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/GECC_research.xlsx
+++ b/app/reports/GECC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.495</v>
+        <v>5.4191</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04549000263214111</v>
+        <v>0.04572999954223633</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>13892044.40400364</v>
+        <v>13892044.06635788</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>5.495</v>
+        <v>5.4191</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>76336784</v>
+        <v>75282376</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
@@ -1511,14 +1511,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>155417712</v>
+        <v>149280112</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>121.8</v>
+        <v>116.990005</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n">
-        <v>2.431</v>
+        <v>2.414</v>
       </c>
     </row>
     <row r="7">
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>79735160</v>
+        <v>79289456</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.518867999999999</v>
+        <v>9.465661000000001</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>4.065</v>
+        <v>4.123</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.403</v>
+        <v>1.423</v>
       </c>
     </row>
     <row r="8">
@@ -1557,14 +1557,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>6831612928</v>
+        <v>9528883200</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-68.764</v>
+        <v>-80.76900000000001</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>680.705</v>
+        <v>799.5410000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1595,12 +1595,12 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>49036972</v>
+        <v>49438912</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>6.238</v>
+        <v>6.261</v>
       </c>
     </row>
     <row r="11">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C11" s="32" t="n"/>
       <c r="D11" s="33" t="n">
-        <v>16.167612</v>
+        <v>15.898665</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
@@ -1633,12 +1633,12 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>85034592</v>
+        <v>84068096</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>9.441000000000001</v>
+        <v>9.096</v>
       </c>
     </row>
     <row r="13">
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>44935904</v>
+        <v>42653568</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-2.799</v>
+        <v>-2.719</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-6.934</v>
+        <v>-6.736</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/GECC_research.xlsx
+++ b/app/reports/GECC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-16 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.4191</v>
+        <v>5.37</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04572999954223633</v>
+        <v>0.04550000190734863</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>13892044.06635788</v>
+        <v>13892044.69273743</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>5.4191</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>75282376</v>
+        <v>74600280</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
@@ -1511,14 +1511,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>149280112</v>
+        <v>148144448</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>116.990005</v>
+        <v>116.1</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n">
-        <v>2.414</v>
+        <v>2.294</v>
       </c>
     </row>
     <row r="7">
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>79289456</v>
+        <v>78954400</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.465661000000001</v>
+        <v>9.425661</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>4.123</v>
+        <v>4.099</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.423</v>
+        <v>1.415</v>
       </c>
     </row>
     <row r="8">
@@ -1557,14 +1557,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>9528883200</v>
+        <v>8587049984</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-80.76900000000001</v>
+        <v>-102.143</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>799.5410000000001</v>
+        <v>1011.126</v>
       </c>
     </row>
     <row r="9">
@@ -1595,12 +1595,12 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>49438912</v>
+        <v>48635028</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>6.261</v>
+        <v>6.258</v>
       </c>
     </row>
     <row r="11">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C11" s="32" t="n"/>
       <c r="D11" s="33" t="n">
-        <v>15.898665</v>
+        <v>15.638123</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>84068096</v>
+        <v>81188520</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>42653568</v>
+        <v>43033956</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-2.719</v>
+        <v>-2.696</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-6.736</v>
+        <v>-6.679</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/GECC_research.xlsx
+++ b/app/reports/GECC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-17 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-18 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>5.37</v>
+        <v>5.34</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04550000190734863</v>
+        <v>0.04540999889373779</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>13892044.69273743</v>
+        <v>13892044.94382023</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>5.37</v>
+        <v>5.34</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>74600280</v>
+        <v>74183520</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n"/>
@@ -1511,14 +1511,14 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>148144448</v>
+        <v>145209648</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>116.1</v>
+        <v>113.8</v>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n">
-        <v>2.294</v>
+        <v>2.265</v>
       </c>
     </row>
     <row r="7">
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>78954400</v>
+        <v>78944912</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>9.425661</v>
+        <v>9.424528</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>4.099</v>
+        <v>4.071</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.415</v>
+        <v>1.405</v>
       </c>
     </row>
     <row r="8">
@@ -1557,14 +1557,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>8587049984</v>
+        <v>8737389568</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-102.143</v>
+        <v>-96.336</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>1011.126</v>
+        <v>953.641</v>
       </c>
     </row>
     <row r="9">
@@ -1595,12 +1595,12 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>48635028</v>
+        <v>46893276</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
       <c r="F10" s="33" t="n">
-        <v>6.258</v>
+        <v>6.197</v>
       </c>
     </row>
     <row r="11">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="C11" s="32" t="n"/>
       <c r="D11" s="33" t="n">
-        <v>15.638123</v>
+        <v>15.592374</v>
       </c>
       <c r="E11" s="33" t="n"/>
       <c r="F11" s="33" t="n"/>
@@ -1633,12 +1633,12 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>81188520</v>
+        <v>88706344</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n"/>
       <c r="F12" s="33" t="n">
-        <v>9.096</v>
+        <v>9.433999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>43033956</v>
+        <v>42265496</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-2.696</v>
+        <v>-2.674</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-6.679</v>
+        <v>-6.622</v>
       </c>
     </row>
     <row r="15">
